--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk1pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk1pct_wu500000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>153154</t>
+          <t>150824</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>296709</t>
+          <t>147761</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>293527</t>
+          <t>147642</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>311848</t>
+          <t>166082</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>320149</t>
+          <t>155943</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>299628</t>
+          <t>145561</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>289246</t>
+          <t>145561</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
